--- a/data/availability/projects/palm-hills-developments/badya.xlsx
+++ b/data/availability/projects/palm-hills-developments/badya.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for badya</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1169,6 @@
       <c r="G2" t="n">
         <v>127.14</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1216,7 +1225,6 @@
       <c r="G3" t="n">
         <v>127.14</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1273,7 +1281,6 @@
       <c r="G4" t="n">
         <v>154.67</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1330,7 +1337,6 @@
       <c r="G5" t="n">
         <v>131.32</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1387,7 +1393,6 @@
       <c r="G6" t="n">
         <v>125.1</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1444,7 +1449,6 @@
       <c r="G7" t="n">
         <v>131.32</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1501,7 +1505,6 @@
       <c r="G8" t="n">
         <v>125.1</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1558,7 +1561,6 @@
       <c r="G9" t="n">
         <v>125.1</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1615,7 +1617,6 @@
       <c r="G10" t="n">
         <v>125.1</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1672,7 +1673,6 @@
       <c r="G11" t="n">
         <v>114.56</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1729,7 +1729,6 @@
       <c r="G12" t="n">
         <v>127.14</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1786,7 +1785,6 @@
       <c r="G13" t="n">
         <v>127.14</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1843,7 +1841,6 @@
       <c r="G14" t="n">
         <v>125.1</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1900,7 +1897,6 @@
       <c r="G15" t="n">
         <v>131.32</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1957,7 +1953,6 @@
       <c r="G16" t="n">
         <v>125.1</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2014,7 +2009,6 @@
       <c r="G17" t="n">
         <v>154.67</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2071,7 +2065,6 @@
       <c r="G18" t="n">
         <v>131.32</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2128,7 +2121,6 @@
       <c r="G19" t="n">
         <v>131.32</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2185,7 +2177,6 @@
       <c r="G20" t="n">
         <v>125.1</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2242,7 +2233,6 @@
       <c r="G21" t="n">
         <v>114.56</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2299,7 +2289,6 @@
       <c r="G22" t="n">
         <v>127.14</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2356,7 +2345,6 @@
       <c r="G23" t="n">
         <v>127.14</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2413,7 +2401,6 @@
       <c r="G24" t="n">
         <v>133.03</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2470,7 +2457,6 @@
       <c r="G25" t="n">
         <v>134.66</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2527,7 +2513,6 @@
       <c r="G26" t="n">
         <v>131.87</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2584,7 +2569,6 @@
       <c r="G27" t="n">
         <v>131.87</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2641,7 +2625,6 @@
       <c r="G28" t="n">
         <v>131.87</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2698,7 +2681,6 @@
       <c r="G29" t="n">
         <v>135.02</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2755,7 +2737,6 @@
       <c r="G30" t="n">
         <v>131.87</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2812,7 +2793,6 @@
       <c r="G31" t="n">
         <v>131.87</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2869,7 +2849,6 @@
       <c r="G32" t="n">
         <v>131.87</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2926,7 +2905,6 @@
       <c r="G33" t="n">
         <v>131.87</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2983,7 +2961,6 @@
       <c r="G34" t="n">
         <v>135.02</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3040,7 +3017,6 @@
       <c r="G35" t="n">
         <v>160.02</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3097,7 +3073,6 @@
       <c r="G36" t="n">
         <v>152.05</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3154,7 +3129,6 @@
       <c r="G37" t="n">
         <v>152.05</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3211,7 +3185,6 @@
       <c r="G38" t="n">
         <v>127.14</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3268,7 +3241,6 @@
       <c r="G39" t="n">
         <v>152.05</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3325,7 +3297,6 @@
       <c r="G40" t="n">
         <v>127.14</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3382,7 +3353,6 @@
       <c r="G41" t="n">
         <v>151.07</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3439,7 +3409,6 @@
       <c r="G42" t="n">
         <v>160.02</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3496,7 +3465,6 @@
       <c r="G43" t="n">
         <v>147.12</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3553,7 +3521,6 @@
       <c r="G44" t="n">
         <v>152.05</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3610,7 +3577,6 @@
       <c r="G45" t="n">
         <v>127.14</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3667,7 +3633,6 @@
       <c r="G46" t="n">
         <v>152.05</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3724,7 +3689,6 @@
       <c r="G47" t="n">
         <v>127.14</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3781,7 +3745,6 @@
       <c r="G48" t="n">
         <v>152.05</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3838,7 +3801,6 @@
       <c r="G49" t="n">
         <v>127.14</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3895,7 +3857,6 @@
       <c r="G50" t="n">
         <v>152.05</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3952,7 +3913,6 @@
       <c r="G51" t="n">
         <v>127.14</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4009,7 +3969,6 @@
       <c r="G52" t="n">
         <v>151.07</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4066,7 +4025,6 @@
       <c r="G53" t="n">
         <v>121.85</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4123,7 +4081,6 @@
       <c r="G54" t="n">
         <v>127.14</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4180,7 +4137,6 @@
       <c r="G55" t="n">
         <v>127.14</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4237,7 +4193,6 @@
       <c r="G56" t="n">
         <v>160.02</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4294,7 +4249,6 @@
       <c r="G57" t="n">
         <v>151.07</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4351,7 +4305,6 @@
       <c r="G58" t="n">
         <v>131.32</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4408,7 +4361,6 @@
       <c r="G59" t="n">
         <v>125.1</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4465,7 +4417,6 @@
       <c r="G60" t="n">
         <v>131.32</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4522,7 +4473,6 @@
       <c r="G61" t="n">
         <v>125.1</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4579,7 +4529,6 @@
       <c r="G62" t="n">
         <v>131.32</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4636,7 +4585,6 @@
       <c r="G63" t="n">
         <v>125.1</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4693,7 +4641,6 @@
       <c r="G64" t="n">
         <v>125.1</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4750,7 +4697,6 @@
       <c r="G65" t="n">
         <v>131.32</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4807,7 +4753,6 @@
       <c r="G66" t="n">
         <v>125.1</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4864,7 +4809,6 @@
       <c r="G67" t="n">
         <v>107.91</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4921,7 +4865,6 @@
       <c r="G68" t="n">
         <v>114.56</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4978,7 +4921,6 @@
       <c r="G69" t="n">
         <v>131.87</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5035,7 +4977,6 @@
       <c r="G70" t="n">
         <v>131.87</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5092,7 +5033,6 @@
       <c r="G71" t="n">
         <v>134.66</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5149,7 +5089,6 @@
       <c r="G72" t="n">
         <v>131.87</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5206,7 +5145,6 @@
       <c r="G73" t="n">
         <v>131.87</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5263,7 +5201,6 @@
       <c r="G74" t="n">
         <v>110.25</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5320,7 +5257,6 @@
       <c r="G75" t="n">
         <v>135.02</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5377,7 +5313,6 @@
       <c r="G76" t="n">
         <v>125.5</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5434,7 +5369,6 @@
       <c r="G77" t="n">
         <v>125.5</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5491,7 +5425,6 @@
       <c r="G78" t="n">
         <v>125.5</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5548,7 +5481,6 @@
       <c r="G79" t="n">
         <v>125.5</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5605,7 +5537,6 @@
       <c r="G80" t="n">
         <v>119.5</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5662,7 +5593,6 @@
       <c r="G81" t="n">
         <v>162.5</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5719,7 +5649,6 @@
       <c r="G82" t="n">
         <v>125.5</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5776,7 +5705,6 @@
       <c r="G83" t="n">
         <v>125.5</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5833,7 +5761,6 @@
       <c r="G84" t="n">
         <v>125.5</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5890,7 +5817,6 @@
       <c r="G85" t="n">
         <v>125.5</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5947,7 +5873,6 @@
       <c r="G86" t="n">
         <v>119.5</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6004,7 +5929,6 @@
       <c r="G87" t="n">
         <v>127</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6061,7 +5985,6 @@
       <c r="G88" t="n">
         <v>125.5</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6118,7 +6041,6 @@
       <c r="G89" t="n">
         <v>125.5</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6175,7 +6097,6 @@
       <c r="G90" t="n">
         <v>125.5</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6232,7 +6153,6 @@
       <c r="G91" t="n">
         <v>125.5</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6289,7 +6209,6 @@
       <c r="G92" t="n">
         <v>124</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6346,7 +6265,6 @@
       <c r="G93" t="n">
         <v>124</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6403,7 +6321,6 @@
       <c r="G94" t="n">
         <v>124</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6460,7 +6377,6 @@
       <c r="G95" t="n">
         <v>124</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6517,7 +6433,6 @@
       <c r="G96" t="n">
         <v>127</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6574,7 +6489,6 @@
       <c r="G97" t="n">
         <v>125.5</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6631,7 +6545,6 @@
       <c r="G98" t="n">
         <v>125.5</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6688,7 +6601,6 @@
       <c r="G99" t="n">
         <v>125.5</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6745,7 +6657,6 @@
       <c r="G100" t="n">
         <v>125.5</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6802,7 +6713,6 @@
       <c r="G101" t="n">
         <v>119.5</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6859,7 +6769,6 @@
       <c r="G102" t="n">
         <v>127</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6916,7 +6825,6 @@
       <c r="G103" t="n">
         <v>125.5</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6973,7 +6881,6 @@
       <c r="G104" t="n">
         <v>125.5</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7030,7 +6937,6 @@
       <c r="G105" t="n">
         <v>125.5</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7087,7 +6993,6 @@
       <c r="G106" t="n">
         <v>125.5</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7144,7 +7049,6 @@
       <c r="G107" t="n">
         <v>119.5</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7201,7 +7105,6 @@
       <c r="G108" t="n">
         <v>194</v>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7258,7 +7161,6 @@
       <c r="G109" t="n">
         <v>151.07</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7315,7 +7217,6 @@
       <c r="G110" t="n">
         <v>127.14</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7372,7 +7273,6 @@
       <c r="G111" t="n">
         <v>154.67</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7429,7 +7329,6 @@
       <c r="G112" t="n">
         <v>125.1</v>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7486,7 +7385,6 @@
       <c r="G113" t="n">
         <v>154.67</v>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7543,7 +7441,6 @@
       <c r="G114" t="n">
         <v>107.91</v>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7600,7 +7497,6 @@
       <c r="G115" t="n">
         <v>133.03</v>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7657,7 +7553,6 @@
       <c r="G116" t="n">
         <v>151.07</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7714,7 +7609,6 @@
       <c r="G117" t="n">
         <v>131.32</v>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7771,7 +7665,6 @@
       <c r="G118" t="n">
         <v>127.14</v>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7828,7 +7721,6 @@
       <c r="G119" t="n">
         <v>131.32</v>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7885,7 +7777,6 @@
       <c r="G120" t="n">
         <v>151.07</v>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7942,7 +7833,6 @@
       <c r="G121" t="n">
         <v>131.32</v>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7999,7 +7889,6 @@
       <c r="G122" t="n">
         <v>154.67</v>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8056,7 +7945,6 @@
       <c r="G123" t="n">
         <v>107.91</v>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8113,7 +8001,6 @@
       <c r="G124" t="n">
         <v>114.56</v>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8170,7 +8057,6 @@
       <c r="G125" t="n">
         <v>135.02</v>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8227,7 +8113,6 @@
       <c r="G126" t="n">
         <v>131.87</v>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8284,7 +8169,6 @@
       <c r="G127" t="n">
         <v>131.32</v>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8341,7 +8225,6 @@
       <c r="G128" t="n">
         <v>125.1</v>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8398,7 +8281,6 @@
       <c r="G129" t="n">
         <v>131.32</v>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8455,7 +8337,6 @@
       <c r="G130" t="n">
         <v>131.32</v>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8512,7 +8393,6 @@
       <c r="G131" t="n">
         <v>107.91</v>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8569,7 +8449,6 @@
       <c r="G132" t="n">
         <v>127.14</v>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8626,7 +8505,6 @@
       <c r="G133" t="n">
         <v>160.02</v>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8683,7 +8561,6 @@
       <c r="G134" t="n">
         <v>131.87</v>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8740,7 +8617,6 @@
       <c r="G135" t="n">
         <v>131.87</v>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8797,7 +8673,6 @@
       <c r="G136" t="n">
         <v>134.66</v>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8854,7 +8729,6 @@
       <c r="G137" t="n">
         <v>127.14</v>
       </c>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8911,7 +8785,6 @@
       <c r="G138" t="n">
         <v>127.14</v>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8968,7 +8841,6 @@
       <c r="G139" t="n">
         <v>131.32</v>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9025,7 +8897,6 @@
       <c r="G140" t="n">
         <v>154.67</v>
       </c>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9082,7 +8953,6 @@
       <c r="G141" t="n">
         <v>154.67</v>
       </c>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9139,7 +9009,6 @@
       <c r="G142" t="n">
         <v>152.05</v>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9196,7 +9065,6 @@
       <c r="G143" t="n">
         <v>127.14</v>
       </c>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9253,7 +9121,6 @@
       <c r="G144" t="n">
         <v>466</v>
       </c>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9310,7 +9177,6 @@
       <c r="G145" t="n">
         <v>194</v>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9367,7 +9233,6 @@
       <c r="G146" t="n">
         <v>190.5</v>
       </c>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9424,7 +9289,6 @@
       <c r="G147" t="n">
         <v>194</v>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9481,7 +9345,6 @@
       <c r="G148" t="n">
         <v>194</v>
       </c>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9538,7 +9401,6 @@
       <c r="G149" t="n">
         <v>194</v>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9595,7 +9457,6 @@
       <c r="G150" t="n">
         <v>364</v>
       </c>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9652,7 +9513,6 @@
       <c r="G151" t="n">
         <v>111.1</v>
       </c>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9709,7 +9569,6 @@
       <c r="G152" t="n">
         <v>111.1</v>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9766,7 +9625,6 @@
       <c r="G153" t="n">
         <v>111.1</v>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9823,7 +9681,6 @@
       <c r="G154" t="n">
         <v>111.1</v>
       </c>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9880,7 +9737,6 @@
       <c r="G155" t="n">
         <v>109.25</v>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9937,7 +9793,6 @@
       <c r="G156" t="n">
         <v>111.65</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9994,7 +9849,6 @@
       <c r="G157" t="n">
         <v>111.65</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10051,7 +9905,6 @@
       <c r="G158" t="n">
         <v>111.65</v>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10108,7 +9961,6 @@
       <c r="G159" t="n">
         <v>111.1</v>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10165,7 +10017,6 @@
       <c r="G160" t="n">
         <v>111.1</v>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10222,7 +10073,6 @@
       <c r="G161" t="n">
         <v>111.1</v>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10279,7 +10129,6 @@
       <c r="G162" t="n">
         <v>111.65</v>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10336,7 +10185,6 @@
       <c r="G163" t="n">
         <v>111.1</v>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10393,7 +10241,6 @@
       <c r="G164" t="n">
         <v>109.25</v>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10450,7 +10297,6 @@
       <c r="G165" t="n">
         <v>109.25</v>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10507,7 +10353,6 @@
       <c r="G166" t="n">
         <v>111.1</v>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10564,7 +10409,6 @@
       <c r="G167" t="n">
         <v>111.1</v>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10621,7 +10465,6 @@
       <c r="G168" t="n">
         <v>111.65</v>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10678,7 +10521,6 @@
       <c r="G169" t="n">
         <v>111.1</v>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10735,7 +10577,6 @@
       <c r="G170" t="n">
         <v>109.25</v>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10792,7 +10633,6 @@
       <c r="G171" t="n">
         <v>109.25</v>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10849,7 +10689,6 @@
       <c r="G172" t="n">
         <v>111.1</v>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10906,7 +10745,6 @@
       <c r="G173" t="n">
         <v>111.65</v>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10963,7 +10801,6 @@
       <c r="G174" t="n">
         <v>111.1</v>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11020,7 +10857,6 @@
       <c r="G175" t="n">
         <v>111.1</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11077,7 +10913,6 @@
       <c r="G176" t="n">
         <v>111.65</v>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11134,7 +10969,6 @@
       <c r="G177" t="n">
         <v>109.25</v>
       </c>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11191,7 +11025,6 @@
       <c r="G178" t="n">
         <v>111.65</v>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11248,7 +11081,6 @@
       <c r="G179" t="n">
         <v>111.1</v>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11305,7 +11137,6 @@
       <c r="G180" t="n">
         <v>111.65</v>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11362,7 +11193,6 @@
       <c r="G181" t="n">
         <v>111.65</v>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11419,7 +11249,6 @@
       <c r="G182" t="n">
         <v>111.65</v>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11476,7 +11305,6 @@
       <c r="G183" t="n">
         <v>111.65</v>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11533,7 +11361,6 @@
       <c r="G184" t="n">
         <v>109.25</v>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11590,7 +11417,6 @@
       <c r="G185" t="n">
         <v>111.65</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11647,7 +11473,6 @@
       <c r="G186" t="n">
         <v>111.65</v>
       </c>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11704,7 +11529,6 @@
       <c r="G187" t="n">
         <v>111.1</v>
       </c>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11761,7 +11585,6 @@
       <c r="G188" t="n">
         <v>111.1</v>
       </c>
-      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11818,7 +11641,6 @@
       <c r="G189" t="n">
         <v>111.65</v>
       </c>
-      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11875,7 +11697,6 @@
       <c r="G190" t="n">
         <v>111.65</v>
       </c>
-      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11932,7 +11753,6 @@
       <c r="G191" t="n">
         <v>111.1</v>
       </c>
-      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11989,7 +11809,6 @@
       <c r="G192" t="n">
         <v>111.1</v>
       </c>
-      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12046,7 +11865,6 @@
       <c r="G193" t="n">
         <v>111.1</v>
       </c>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12103,7 +11921,6 @@
       <c r="G194" t="n">
         <v>111.65</v>
       </c>
-      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12160,7 +11977,6 @@
       <c r="G195" t="n">
         <v>111.1</v>
       </c>
-      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12217,7 +12033,6 @@
       <c r="G196" t="n">
         <v>111.1</v>
       </c>
-      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12274,7 +12089,6 @@
       <c r="G197" t="n">
         <v>111.1</v>
       </c>
-      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12331,7 +12145,6 @@
       <c r="G198" t="n">
         <v>111.1</v>
       </c>
-      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12388,7 +12201,6 @@
       <c r="G199" t="n">
         <v>111.1</v>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12445,7 +12257,6 @@
       <c r="G200" t="n">
         <v>111.1</v>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12502,7 +12313,6 @@
       <c r="G201" t="n">
         <v>111.65</v>
       </c>
-      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12559,7 +12369,6 @@
       <c r="G202" t="n">
         <v>111.1</v>
       </c>
-      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12616,7 +12425,6 @@
       <c r="G203" t="n">
         <v>111.1</v>
       </c>
-      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12673,7 +12481,6 @@
       <c r="G204" t="n">
         <v>111.1</v>
       </c>
-      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12730,7 +12537,6 @@
       <c r="G205" t="n">
         <v>111.65</v>
       </c>
-      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12787,7 +12593,6 @@
       <c r="G206" t="n">
         <v>111.65</v>
       </c>
-      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12844,7 +12649,6 @@
       <c r="G207" t="n">
         <v>111.1</v>
       </c>
-      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12901,7 +12705,6 @@
       <c r="G208" t="n">
         <v>111.1</v>
       </c>
-      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12958,7 +12761,6 @@
       <c r="G209" t="n">
         <v>111.65</v>
       </c>
-      <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13015,7 +12817,6 @@
       <c r="G210" t="n">
         <v>111.1</v>
       </c>
-      <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13072,7 +12873,6 @@
       <c r="G211" t="n">
         <v>111.65</v>
       </c>
-      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13129,7 +12929,6 @@
       <c r="G212" t="n">
         <v>111.1</v>
       </c>
-      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13186,7 +12985,6 @@
       <c r="G213" t="n">
         <v>133.03</v>
       </c>
-      <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13243,7 +13041,6 @@
       <c r="G214" t="n">
         <v>131.87</v>
       </c>
-      <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13300,7 +13097,6 @@
       <c r="G215" t="n">
         <v>125.1</v>
       </c>
-      <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13357,7 +13153,6 @@
       <c r="G216" t="n">
         <v>131.87</v>
       </c>
-      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13414,7 +13209,6 @@
       <c r="G217" t="n">
         <v>121.85</v>
       </c>
-      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13471,7 +13265,6 @@
       <c r="G218" t="n">
         <v>121.85</v>
       </c>
-      <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13528,7 +13321,6 @@
       <c r="G219" t="n">
         <v>125.1</v>
       </c>
-      <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13585,7 +13377,6 @@
       <c r="G220" t="n">
         <v>121.85</v>
       </c>
-      <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13642,7 +13433,6 @@
       <c r="G221" t="n">
         <v>125.1</v>
       </c>
-      <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13699,7 +13489,6 @@
       <c r="G222" t="n">
         <v>125.1</v>
       </c>
-      <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13756,7 +13545,6 @@
       <c r="G223" t="n">
         <v>252.84</v>
       </c>
-      <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13813,7 +13601,6 @@
       <c r="G224" t="n">
         <v>133.03</v>
       </c>
-      <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13870,7 +13657,6 @@
       <c r="G225" t="n">
         <v>252.84</v>
       </c>
-      <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13927,7 +13713,6 @@
       <c r="G226" t="n">
         <v>252.84</v>
       </c>
-      <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13984,7 +13769,6 @@
       <c r="G227" t="n">
         <v>171.19</v>
       </c>
-      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14041,7 +13825,6 @@
       <c r="G228" t="n">
         <v>195.76</v>
       </c>
-      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14098,7 +13881,6 @@
       <c r="G229" t="n">
         <v>171.19</v>
       </c>
-      <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14155,7 +13937,6 @@
       <c r="G230" t="n">
         <v>195.76</v>
       </c>
-      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14212,7 +13993,6 @@
       <c r="G231" t="n">
         <v>245.22</v>
       </c>
-      <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14269,7 +14049,6 @@
       <c r="G232" t="n">
         <v>131.87</v>
       </c>
-      <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14326,7 +14105,6 @@
       <c r="G233" t="n">
         <v>110.25</v>
       </c>
-      <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14383,7 +14161,6 @@
       <c r="G234" t="n">
         <v>133.03</v>
       </c>
-      <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14440,7 +14217,6 @@
       <c r="G235" t="n">
         <v>151.07</v>
       </c>
-      <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14497,7 +14273,6 @@
       <c r="G236" t="n">
         <v>160.02</v>
       </c>
-      <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14554,7 +14329,6 @@
       <c r="G237" t="n">
         <v>127.14</v>
       </c>
-      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14611,7 +14385,6 @@
       <c r="G238" t="n">
         <v>121.85</v>
       </c>
-      <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14668,7 +14441,6 @@
       <c r="G239" t="n">
         <v>114.56</v>
       </c>
-      <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14725,7 +14497,6 @@
       <c r="G240" t="n">
         <v>160.02</v>
       </c>
-      <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14782,7 +14553,6 @@
       <c r="G241" t="n">
         <v>127.14</v>
       </c>
-      <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14839,7 +14609,6 @@
       <c r="G242" t="n">
         <v>127.14</v>
       </c>
-      <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14896,7 +14665,6 @@
       <c r="G243" t="n">
         <v>125.1</v>
       </c>
-      <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14953,7 +14721,6 @@
       <c r="G244" t="n">
         <v>107.91</v>
       </c>
-      <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15010,7 +14777,6 @@
       <c r="G245" t="n">
         <v>114.56</v>
       </c>
-      <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15067,7 +14833,6 @@
       <c r="G246" t="n">
         <v>127.14</v>
       </c>
-      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15124,7 +14889,6 @@
       <c r="G247" t="n">
         <v>160.02</v>
       </c>
-      <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15181,7 +14945,6 @@
       <c r="G248" t="n">
         <v>127.14</v>
       </c>
-      <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15238,7 +15001,6 @@
       <c r="G249" t="n">
         <v>135.02</v>
       </c>
-      <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15295,7 +15057,6 @@
       <c r="G250" t="n">
         <v>133.03</v>
       </c>
-      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15352,7 +15113,6 @@
       <c r="G251" t="n">
         <v>162.5</v>
       </c>
-      <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15409,7 +15169,6 @@
       <c r="G252" t="n">
         <v>127</v>
       </c>
-      <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15466,7 +15225,6 @@
       <c r="G253" t="n">
         <v>125.5</v>
       </c>
-      <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15523,7 +15281,6 @@
       <c r="G254" t="n">
         <v>125.5</v>
       </c>
-      <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15580,7 +15337,6 @@
       <c r="G255" t="n">
         <v>125.5</v>
       </c>
-      <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15637,7 +15393,6 @@
       <c r="G256" t="n">
         <v>125.5</v>
       </c>
-      <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15694,7 +15449,6 @@
       <c r="G257" t="n">
         <v>113.5</v>
       </c>
-      <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15751,7 +15505,6 @@
       <c r="G258" t="n">
         <v>119.5</v>
       </c>
-      <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15808,7 +15561,6 @@
       <c r="G259" t="n">
         <v>162.5</v>
       </c>
-      <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15865,7 +15617,6 @@
       <c r="G260" t="n">
         <v>127</v>
       </c>
-      <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15922,7 +15673,6 @@
       <c r="G261" t="n">
         <v>125.5</v>
       </c>
-      <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15979,7 +15729,6 @@
       <c r="G262" t="n">
         <v>125.5</v>
       </c>
-      <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16036,7 +15785,6 @@
       <c r="G263" t="n">
         <v>125.5</v>
       </c>
-      <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16093,7 +15841,6 @@
       <c r="G264" t="n">
         <v>125.5</v>
       </c>
-      <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16150,7 +15897,6 @@
       <c r="G265" t="n">
         <v>113.5</v>
       </c>
-      <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16207,7 +15953,6 @@
       <c r="G266" t="n">
         <v>119.5</v>
       </c>
-      <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16264,7 +16009,6 @@
       <c r="G267" t="n">
         <v>127</v>
       </c>
-      <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16321,7 +16065,6 @@
       <c r="G268" t="n">
         <v>125.5</v>
       </c>
-      <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16378,7 +16121,6 @@
       <c r="G269" t="n">
         <v>125.5</v>
       </c>
-      <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16435,7 +16177,6 @@
       <c r="G270" t="n">
         <v>125.5</v>
       </c>
-      <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16492,7 +16233,6 @@
       <c r="G271" t="n">
         <v>124</v>
       </c>
-      <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16549,7 +16289,6 @@
       <c r="G272" t="n">
         <v>124</v>
       </c>
-      <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16606,7 +16345,6 @@
       <c r="G273" t="n">
         <v>124</v>
       </c>
-      <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16663,7 +16401,6 @@
       <c r="G274" t="n">
         <v>125.5</v>
       </c>
-      <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16720,7 +16457,6 @@
       <c r="G275" t="n">
         <v>125.5</v>
       </c>
-      <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16777,7 +16513,6 @@
       <c r="G276" t="n">
         <v>125.5</v>
       </c>
-      <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16834,7 +16569,6 @@
       <c r="G277" t="n">
         <v>125.5</v>
       </c>
-      <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16891,7 +16625,6 @@
       <c r="G278" t="n">
         <v>190.5</v>
       </c>
-      <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16948,7 +16681,6 @@
       <c r="G279" t="n">
         <v>190.5</v>
       </c>
-      <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17005,7 +16737,6 @@
       <c r="G280" t="n">
         <v>194</v>
       </c>
-      <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17062,7 +16793,6 @@
       <c r="G281" t="n">
         <v>190.5</v>
       </c>
-      <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17119,7 +16849,6 @@
       <c r="G282" t="n">
         <v>194</v>
       </c>
-      <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17176,7 +16905,6 @@
       <c r="G283" t="n">
         <v>194</v>
       </c>
-      <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17233,7 +16961,6 @@
       <c r="G284" t="n">
         <v>194</v>
       </c>
-      <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17290,7 +17017,6 @@
       <c r="G285" t="n">
         <v>194</v>
       </c>
-      <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17347,7 +17073,6 @@
       <c r="G286" t="n">
         <v>190.5</v>
       </c>
-      <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17404,7 +17129,6 @@
       <c r="G287" t="n">
         <v>190.5</v>
       </c>
-      <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17461,7 +17185,6 @@
       <c r="G288" t="n">
         <v>190.5</v>
       </c>
-      <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17518,7 +17241,6 @@
       <c r="G289" t="n">
         <v>194</v>
       </c>
-      <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17575,7 +17297,6 @@
       <c r="G290" t="n">
         <v>194</v>
       </c>
-      <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17632,7 +17353,6 @@
       <c r="G291" t="n">
         <v>194</v>
       </c>
-      <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17689,7 +17409,6 @@
       <c r="G292" t="n">
         <v>190.5</v>
       </c>
-      <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17746,7 +17465,6 @@
       <c r="G293" t="n">
         <v>190.5</v>
       </c>
-      <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17803,7 +17521,6 @@
       <c r="G294" t="n">
         <v>194</v>
       </c>
-      <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17860,7 +17577,6 @@
       <c r="G295" t="n">
         <v>190.5</v>
       </c>
-      <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17917,7 +17633,6 @@
       <c r="G296" t="n">
         <v>190.5</v>
       </c>
-      <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17974,7 +17689,6 @@
       <c r="G297" t="n">
         <v>194</v>
       </c>
-      <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18031,7 +17745,6 @@
       <c r="G298" t="n">
         <v>194</v>
       </c>
-      <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18088,7 +17801,6 @@
       <c r="G299" t="n">
         <v>190.5</v>
       </c>
-      <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18145,7 +17857,6 @@
       <c r="G300" t="n">
         <v>190.5</v>
       </c>
-      <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18202,7 +17913,6 @@
       <c r="G301" t="n">
         <v>194</v>
       </c>
-      <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18259,7 +17969,6 @@
       <c r="G302" t="n">
         <v>194</v>
       </c>
-      <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18316,7 +18025,6 @@
       <c r="G303" t="n">
         <v>194</v>
       </c>
-      <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18373,7 +18081,6 @@
       <c r="G304" t="n">
         <v>194</v>
       </c>
-      <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18430,7 +18137,6 @@
       <c r="G305" t="n">
         <v>190.5</v>
       </c>
-      <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18487,7 +18193,6 @@
       <c r="G306" t="n">
         <v>190.5</v>
       </c>
-      <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18544,7 +18249,6 @@
       <c r="G307" t="n">
         <v>194</v>
       </c>
-      <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18601,7 +18305,6 @@
       <c r="G308" t="n">
         <v>180</v>
       </c>
-      <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18658,7 +18361,6 @@
       <c r="G309" t="n">
         <v>180</v>
       </c>
-      <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18715,7 +18417,6 @@
       <c r="G310" t="n">
         <v>180</v>
       </c>
-      <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18772,7 +18473,6 @@
       <c r="G311" t="n">
         <v>180</v>
       </c>
-      <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18829,7 +18529,6 @@
       <c r="G312" t="n">
         <v>180</v>
       </c>
-      <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18886,7 +18585,6 @@
       <c r="G313" t="n">
         <v>364</v>
       </c>
-      <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18943,7 +18641,6 @@
       <c r="G314" t="n">
         <v>364</v>
       </c>
-      <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19000,7 +18697,6 @@
       <c r="G315" t="n">
         <v>180</v>
       </c>
-      <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19057,7 +18753,6 @@
       <c r="G316" t="n">
         <v>180</v>
       </c>
-      <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19114,7 +18809,6 @@
       <c r="G317" t="n">
         <v>275.5</v>
       </c>
-      <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19171,7 +18865,6 @@
       <c r="G318" t="n">
         <v>275.5</v>
       </c>
-      <c r="H318" t="inlineStr"/>
       <c r="I318" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19228,7 +18921,6 @@
       <c r="G319" t="n">
         <v>275.5</v>
       </c>
-      <c r="H319" t="inlineStr"/>
       <c r="I319" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19285,7 +18977,6 @@
       <c r="G320" t="n">
         <v>275.5</v>
       </c>
-      <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19342,7 +19033,6 @@
       <c r="G321" t="n">
         <v>466</v>
       </c>
-      <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19399,7 +19089,6 @@
       <c r="G322" t="n">
         <v>466</v>
       </c>
-      <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19456,7 +19145,6 @@
       <c r="G323" t="n">
         <v>466</v>
       </c>
-      <c r="H323" t="inlineStr"/>
       <c r="I323" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19513,7 +19201,6 @@
       <c r="G324" t="n">
         <v>466</v>
       </c>
-      <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19570,7 +19257,6 @@
       <c r="G325" t="n">
         <v>466</v>
       </c>
-      <c r="H325" t="inlineStr"/>
       <c r="I325" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19627,7 +19313,6 @@
       <c r="G326" t="n">
         <v>180</v>
       </c>
-      <c r="H326" t="inlineStr"/>
       <c r="I326" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19684,7 +19369,6 @@
       <c r="G327" t="n">
         <v>180</v>
       </c>
-      <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19741,7 +19425,6 @@
       <c r="G328" t="n">
         <v>180</v>
       </c>
-      <c r="H328" t="inlineStr"/>
       <c r="I328" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19798,7 +19481,6 @@
       <c r="G329" t="n">
         <v>180</v>
       </c>
-      <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19855,7 +19537,6 @@
       <c r="G330" t="n">
         <v>364</v>
       </c>
-      <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19912,7 +19593,6 @@
       <c r="G331" t="n">
         <v>364</v>
       </c>
-      <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19969,7 +19649,6 @@
       <c r="G332" t="n">
         <v>364</v>
       </c>
-      <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20026,7 +19705,6 @@
       <c r="G333" t="n">
         <v>364</v>
       </c>
-      <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20083,7 +19761,6 @@
       <c r="G334" t="n">
         <v>364</v>
       </c>
-      <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20140,7 +19817,6 @@
       <c r="G335" t="n">
         <v>275.5</v>
       </c>
-      <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20197,7 +19873,6 @@
       <c r="G336" t="n">
         <v>466</v>
       </c>
-      <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20254,7 +19929,6 @@
       <c r="G337" t="n">
         <v>466</v>
       </c>
-      <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20311,7 +19985,6 @@
       <c r="G338" t="n">
         <v>466</v>
       </c>
-      <c r="H338" t="inlineStr"/>
       <c r="I338" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20368,7 +20041,6 @@
       <c r="G339" t="n">
         <v>466</v>
       </c>
-      <c r="H339" t="inlineStr"/>
       <c r="I339" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20425,7 +20097,6 @@
       <c r="G340" t="n">
         <v>364</v>
       </c>
-      <c r="H340" t="inlineStr"/>
       <c r="I340" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20482,7 +20153,6 @@
       <c r="G341" t="n">
         <v>364</v>
       </c>
-      <c r="H341" t="inlineStr"/>
       <c r="I341" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20539,7 +20209,6 @@
       <c r="G342" t="n">
         <v>364</v>
       </c>
-      <c r="H342" t="inlineStr"/>
       <c r="I342" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20596,7 +20265,6 @@
       <c r="G343" t="n">
         <v>364</v>
       </c>
-      <c r="H343" t="inlineStr"/>
       <c r="I343" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20653,7 +20321,6 @@
       <c r="G344" t="n">
         <v>364</v>
       </c>
-      <c r="H344" t="inlineStr"/>
       <c r="I344" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20710,7 +20377,6 @@
       <c r="G345" t="n">
         <v>466</v>
       </c>
-      <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20767,7 +20433,6 @@
       <c r="G346" t="n">
         <v>466</v>
       </c>
-      <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20824,7 +20489,6 @@
       <c r="G347" t="n">
         <v>364</v>
       </c>
-      <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20881,7 +20545,6 @@
       <c r="G348" t="n">
         <v>180</v>
       </c>
-      <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20938,7 +20601,6 @@
       <c r="G349" t="n">
         <v>180</v>
       </c>
-      <c r="H349" t="inlineStr"/>
       <c r="I349" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20995,7 +20657,6 @@
       <c r="G350" t="n">
         <v>180</v>
       </c>
-      <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21052,7 +20713,6 @@
       <c r="G351" t="n">
         <v>180</v>
       </c>
-      <c r="H351" t="inlineStr"/>
       <c r="I351" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21109,7 +20769,6 @@
       <c r="G352" t="n">
         <v>180</v>
       </c>
-      <c r="H352" t="inlineStr"/>
       <c r="I352" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21166,7 +20825,6 @@
       <c r="G353" t="n">
         <v>180</v>
       </c>
-      <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21223,7 +20881,6 @@
       <c r="G354" t="n">
         <v>180</v>
       </c>
-      <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21280,7 +20937,6 @@
       <c r="G355" t="n">
         <v>180</v>
       </c>
-      <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr">
         <is>
           <t>Landscape</t>

--- a/data/availability/projects/palm-hills-developments/badya.xlsx
+++ b/data/availability/projects/palm-hills-developments/badya.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -697,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -747,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -797,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6387,7 +6387,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9299,7 +9299,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -10755,7 +10755,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -11147,7 +11147,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -12043,7 +12043,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -12267,7 +12267,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -12379,7 +12379,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -12715,7 +12715,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -13611,7 +13611,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -13723,7 +13723,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -14059,7 +14059,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -14171,7 +14171,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -14283,7 +14283,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -14339,7 +14339,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -14395,7 +14395,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -14507,7 +14507,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -14787,7 +14787,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -14843,7 +14843,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -14955,7 +14955,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -15011,7 +15011,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -15179,7 +15179,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -15235,7 +15235,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -15347,7 +15347,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -15515,7 +15515,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -15627,7 +15627,7 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -15907,7 +15907,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -15963,7 +15963,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -16019,7 +16019,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -16075,7 +16075,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -16187,7 +16187,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -16523,7 +16523,7 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -16579,7 +16579,7 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -16601,7 +16601,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -16635,7 +16635,7 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -16747,7 +16747,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -16769,7 +16769,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -16825,7 +16825,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -16859,7 +16859,7 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -16881,7 +16881,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -16915,7 +16915,7 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -16971,7 +16971,7 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -16993,7 +16993,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17027,7 +17027,7 @@
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -17049,7 +17049,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17083,7 +17083,7 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -17139,7 +17139,7 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -17161,7 +17161,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -17195,7 +17195,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -17217,7 +17217,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -17251,7 +17251,7 @@
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -17273,7 +17273,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -17307,7 +17307,7 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -17329,7 +17329,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -17363,7 +17363,7 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -17419,7 +17419,7 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -17475,7 +17475,7 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -17497,7 +17497,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -17587,7 +17587,7 @@
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -17609,7 +17609,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -17643,7 +17643,7 @@
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -17665,7 +17665,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -17721,7 +17721,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -17777,7 +17777,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -17811,7 +17811,7 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -17833,7 +17833,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -17867,7 +17867,7 @@
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -17889,7 +17889,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -17923,7 +17923,7 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -17945,7 +17945,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -17979,7 +17979,7 @@
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -18035,7 +18035,7 @@
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -18057,7 +18057,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -18091,7 +18091,7 @@
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -18113,7 +18113,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -18147,7 +18147,7 @@
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -18169,7 +18169,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -18203,7 +18203,7 @@
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -18225,7 +18225,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -18281,7 +18281,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -18337,7 +18337,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -18371,7 +18371,7 @@
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -18393,7 +18393,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -18427,7 +18427,7 @@
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -18449,7 +18449,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -18505,7 +18505,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -18539,7 +18539,7 @@
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -18561,7 +18561,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -18617,7 +18617,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -18651,7 +18651,7 @@
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
@@ -18673,7 +18673,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -18707,7 +18707,7 @@
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -18729,7 +18729,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -18763,7 +18763,7 @@
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -18785,7 +18785,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -18819,7 +18819,7 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -18841,7 +18841,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -18875,7 +18875,7 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -18897,7 +18897,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -18931,7 +18931,7 @@
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -18953,7 +18953,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -18987,7 +18987,7 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -19009,7 +19009,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -19043,7 +19043,7 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -19065,7 +19065,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -19121,7 +19121,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -19155,7 +19155,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -19177,7 +19177,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -19211,7 +19211,7 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -19233,7 +19233,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -19267,7 +19267,7 @@
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -19289,7 +19289,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -19323,7 +19323,7 @@
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -19345,7 +19345,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -19379,7 +19379,7 @@
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -19435,7 +19435,7 @@
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -19457,7 +19457,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
@@ -19513,7 +19513,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -19569,7 +19569,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -19625,7 +19625,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -19659,7 +19659,7 @@
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -19681,7 +19681,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -19737,7 +19737,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -19771,7 +19771,7 @@
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -19793,7 +19793,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -19827,7 +19827,7 @@
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -19849,7 +19849,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -19883,7 +19883,7 @@
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -19905,7 +19905,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -19939,7 +19939,7 @@
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -19961,7 +19961,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -19995,7 +19995,7 @@
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -20017,7 +20017,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -20073,7 +20073,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -20107,7 +20107,7 @@
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -20129,7 +20129,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -20163,7 +20163,7 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -20185,7 +20185,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -20219,7 +20219,7 @@
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -20275,7 +20275,7 @@
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -20297,7 +20297,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -20331,7 +20331,7 @@
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
@@ -20353,7 +20353,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -20387,7 +20387,7 @@
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -20409,7 +20409,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -20443,7 +20443,7 @@
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -20465,7 +20465,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -20521,7 +20521,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -20555,7 +20555,7 @@
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -20577,7 +20577,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -20611,7 +20611,7 @@
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -20667,7 +20667,7 @@
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -20689,7 +20689,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -20723,7 +20723,7 @@
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -20745,7 +20745,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -20779,7 +20779,7 @@
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -20835,7 +20835,7 @@
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
@@ -20913,7 +20913,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -20947,7 +20947,7 @@
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
